--- a/education_forms/050_speaker_information_collection_form--education_forms.xlsx
+++ b/education_forms/050_speaker_information_collection_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'no_image',_'value':_'no_image'}</t>
+          <t>no_image</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'No Image', 'value': 'no_image'}</t>
+          <t>No Image</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'image',_'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Image', 'value': 'image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_16,_'label':_'facebook',_'value':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 16, 'label': 'Facebook', 'value': 'facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_17,_'label':_'twitter',_'value':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 17, 'label': 'Twitter', 'value': 'twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_18,_'label':_'linkedin',_'value':_'linkedin'}</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 18, 'label': 'LinkedIn', 'value': 'linkedin'}</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_19,_'label':_'instagram',_'value':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 19, 'label': 'Instagram', 'value': 'instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'youtube',_'value':_'youtube'}</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'YouTube', 'value': 'youtube'}</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'keynote',_'value':_'keynote'}</t>
+          <t>keynote</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Keynote', 'value': 'keynote'}</t>
+          <t>Keynote</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_22,_'label':_'panel',_'value':_'panel'}</t>
+          <t>panel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 22, 'label': 'Panel', 'value': 'panel'}</t>
+          <t>Panel</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'workshop',_'value':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Workshop', 'value': 'workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'breakout',_'value':_'breakout'}</t>
+          <t>breakout</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Breakout', 'value': 'breakout'}</t>
+          <t>Breakout</t>
         </is>
       </c>
     </row>
